--- a/Weekly Reporting SEPT 1.xlsx
+++ b/Weekly Reporting SEPT 1.xlsx
@@ -581,27 +581,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -936,745 +936,753 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="3" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="4"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="3" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="3" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="3" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="4"/>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="3" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="3" t="s">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="3" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3" t="s">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="3" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="4"/>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="9"/>
+      <c r="B26" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="3" t="s">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="3" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="3" t="s">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="3" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="3" t="s">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="3" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="4"/>
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="9"/>
+      <c r="B34" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="3" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="3" t="s">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="3" t="s">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="3" t="s">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="3" t="s">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="3" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="4"/>
-      <c r="B42" s="2" t="s">
+      <c r="A42" s="9"/>
+      <c r="B42" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="3" t="s">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="2">
         <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="3" t="s">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="2">
         <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="3" t="s">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
     <mergeCell ref="A38:A45"/>
     <mergeCell ref="B38:B41"/>
     <mergeCell ref="B42:B45"/>
@@ -1684,14 +1692,6 @@
     <mergeCell ref="A30:A37"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B34:B37"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1724,215 +1724,215 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>182</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>240</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="5">
         <v>0.76</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>257</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>240</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="4">
         <v>1.07</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>70</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>240</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="5">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>301</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>240</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="4">
         <v>1.25</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>192</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>240</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>196</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>240</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>0.82</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>281</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>240</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <v>1.17</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>223</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>240</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="4">
         <v>0.93</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>150</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>240</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="5">
         <v>0.62</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>195</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>240</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>0.81</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>149</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>240</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="5">
         <v>0.62</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="3">
+      <c r="B13" s="11"/>
+      <c r="C13" s="2">
         <v>2196</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>2640</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="7" t="s">
         <v>142</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Weekly Reporting SEPT 1.xlsx
+++ b/Weekly Reporting SEPT 1.xlsx
@@ -9,18 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Résumé Ventes" sheetId="1" r:id="rId1"/>
     <sheet name="Ventes Par PVT" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="144">
   <si>
     <t>DRV</t>
   </si>
@@ -1675,14 +1675,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
     <mergeCell ref="A38:A45"/>
     <mergeCell ref="B38:B41"/>
     <mergeCell ref="B42:B45"/>
@@ -1692,6 +1684,14 @@
     <mergeCell ref="A30:A37"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1699,14 +1699,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="2" max="2" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1739,8 +1739,11 @@
       <c r="E2" s="5">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>20</v>
       </c>
@@ -1756,8 +1759,11 @@
       <c r="E3" s="4">
         <v>1.07</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>20</v>
       </c>
@@ -1774,7 +1780,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>46</v>
       </c>
@@ -1791,7 +1797,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>46</v>
       </c>
@@ -1808,7 +1814,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>72</v>
       </c>
@@ -1825,7 +1831,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>72</v>
       </c>
@@ -1842,7 +1848,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>96</v>
       </c>
@@ -1859,7 +1865,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>96</v>
       </c>
@@ -1876,7 +1882,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>118</v>
       </c>
@@ -1893,7 +1899,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>118</v>
       </c>
@@ -1910,7 +1916,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>143</v>
       </c>
